--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_skillTree/lang_skillTree__name_title__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_skillTree/lang_skillTree__name_title__part_0001.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="translation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'translation'!$A$1:$N$22</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -25,23 +28,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,33 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -440,6 +431,22 @@
   </sheetPr>
   <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -514,1480 +521,1481 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059064</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>SkillCondition</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Activate predecessor node to unlock</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Kích hoạt nút tiền nhiệm để mở khóa</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059065</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Of Wind and Feathers</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Của Gió và Lông Vũ</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Of Wind and Feathers</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059066</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>The Ever Burning Flame</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>The Ever Burning Flame</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059067</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Vessel of Sound</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Vessel of Sound</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>translate_ambiguous_name_title</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059068</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Snow Dance Flora</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Snow Dance Flora</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059069</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Power of Xuanwu</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Power of Xuanwu</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>translate_ambiguous_name_title</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059070</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Vessel of Sound</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Vessel of Sound</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>translate_ambiguous_name_title</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059071</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Sadness Enshroud</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Sadness Enshroud</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059072</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Yin Yang Sheep</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Yin Yang Sheep</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059073</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>RoleSkillTreeInfo</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Crimson Blades</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Crimson Blades</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059074</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Floating Sound Wave: {0}</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Floating Sound Wave: {0}</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059075</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Extreme Sound: {0} after fully charging</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Âm Cực: {0} sau khi sạc đầy</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Extreme Sound: {0} sau khi sạc đầy</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059076</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Stifle Fire: Hold {0} when have Thermobaric Bullet remain.
 Boom: Tap {1} after consuming 50 Thermobaric Bullets.</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Dập Lửa: Giữ {0} khi còn Đạn Nhiệt Áp.
-Nổ: Nhấn {1} sau khi tiêu hao 50 Đạn Nhiệt Áp.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Dập lửa: Giữ {0} khi còn đạn Thermobaric.
+Bùng nổ: Nhấn {1} sau khi tiêu hao 50 viên đạn Thermobaric.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059077</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Fighting Spirit: Tap {0}</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Fighting Spirit: Chạm {0}</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Fighting Spirit: Tap {0}</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059078</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Let It Burn: {0} after fully charged</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Để Nó Cháy: {0} sau khi sạc đầy</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Let It Burn: {0} sau khi sạc đầy</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059079</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Sound of the Winds - Wind Strike: Hold {0} when having 3 Cleaving Winds.
 Sound of the Winds - Wind Strike: Tap {0} in midair when having 3 Cleaving Winds.</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Âm Gió - Đòn Gió: Giữ {0} khi có 3 Lưỡi Gió Xé.
-Âm Gió - Đòn Gió: Nhấn {0} giữa không khi có 3 Lưỡi Gió Xé.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Âm thanh gió - Đòn gió: Giữ {0} khi có 3 Cleaving Winds.
+Âm thanh gió - Đòn gió: Nhấn {0} giữa không trung khi có 3 Cleaving Winds.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059080</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Carrying Winds: {0}</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Carrying Winds: {0}</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059081</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>New Wind Breeze: {0} after fully charging</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Luồng Gió Mới: {0} sau khi sạc đầy</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>New Wind Breeze: {0} sau khi sạc đầy</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059082</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Icy Lotus: {0} when having Chilling Veins remain.</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Hoa Sen Băng: {0} khi còn Tĩnh Mạch Lạnh.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Icy Lotus: {0} khi còn Chilling Veins.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>translate_short_title</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059083</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Fading Warmth: {0}</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Fading Warmth: {0}</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>NAME_TITLE_0059084</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>name_title</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>name_title_prompt.md</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.json</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>lang_skillTree.db</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>SkillInput</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Fading Warmth: {0}</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Fading Warmth: {0}</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>keep_proper_name</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:N22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>